--- a/output/pdf_financials_xlsx/SF.xlsx
+++ b/output/pdf_financials_xlsx/SF.xlsx
@@ -5930,19 +5930,19 @@
         <v>0</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>7.309121</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>6.974897</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>10.543512</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>10.543512</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>10.543512</v>
       </c>
     </row>
     <row r="92">
@@ -11302,7 +11302,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -15070,7 +15074,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SF.xlsx
+++ b/output/pdf_financials_xlsx/SF.xlsx
@@ -961,22 +961,22 @@
         <v>0.826873</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.44963</v>
+        <v>2.436662</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.451489</v>
+        <v>1.49468</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.556738</v>
+        <v>1.838387</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.287016</v>
+        <v>3.878706</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.053027</v>
+        <v>2.720418</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.80163</v>
+        <v>2.793202</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.7888770000000001</v>
@@ -1023,22 +1023,22 @@
         <v>-0.826873</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.44963</v>
+        <v>-2.436662</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.451489</v>
+        <v>-1.49468</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.556738</v>
+        <v>-1.838387</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-1.287016</v>
+        <v>-3.878706</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.053027</v>
+        <v>-2.720418</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.80163</v>
+        <v>-2.793202</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-0.7888770000000001</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.022169</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1105,16 +1105,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.003962</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.004946</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.249649</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.463913</v>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.354938</v>
+        <v>-0.377107</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.129882</v>
+        <v>-0.12989</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.122806</v>
@@ -2095,16 +2095,16 @@
         <v>-2.928617</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-6.504463</v>
+        <v>-6.508425</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.697656</v>
+        <v>-5.702602</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-18.214284</v>
+        <v>-18.463933</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.268512</v>
+        <v>-2.732425</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.354938</v>
+        <v>-0.377107</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.129882</v>
+        <v>-0.12989</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.121927</v>
@@ -2219,16 +2219,16 @@
         <v>-2.921169</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-6.48604</v>
+        <v>-6.490002</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.503371</v>
+        <v>-5.508317</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-17.667887</v>
+        <v>-17.917536</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.227027</v>
+        <v>-0.69094</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-1861.35679323721</v>
+        <v>-1887.657949797407</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-2.36802021694118</v>
+        <v>-7.20689560577966</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.008791</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000188</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.06432599999999999</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.42219</v>
@@ -2506,37 +2506,37 @@
         <v>1.539965</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.999251</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.03912</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.39187</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.028138</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.56569</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.051421</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.649967</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.319867</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>20.732663</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.416916</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.037235</v>
       </c>
     </row>
     <row r="35">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.008791</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000188</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.06432599999999999</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.42219</v>
@@ -2622,37 +2622,37 @@
         <v>1.539965</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.999251</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.03912</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.39187</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.028138</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.56569</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.051421</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.649967</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.319867</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>20.732663</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.416916</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.037235</v>
       </c>
     </row>
     <row r="37">
@@ -3300,13 +3300,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.008791</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.102688</v>
+        <v>0.1025</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.189995</v>
+        <v>1.125669</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.822462</v>
@@ -3318,37 +3318,37 @@
         <v>0.031512</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.020374</v>
+        <v>0.021123</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.04812</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.44152</v>
+        <v>0.04965</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.044249</v>
+        <v>0.016111</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.572423</v>
+        <v>0.006733</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.072178</v>
+        <v>0.020757</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.670678</v>
+        <v>0.020711</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.7427049999999999</v>
+        <v>0.422838</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>20.794265</v>
+        <v>0.061602</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.569152</v>
+        <v>0.152236</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>35.703767</v>
+        <v>34.666532</v>
       </c>
     </row>
     <row r="49">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -25239,7 +25239,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -62647,7 +62647,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -62746,7 +62746,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -66831,7 +66831,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -74750,7 +74750,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -75920,7 +75920,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -76015,7 +76015,7 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -78136,7 +78136,7 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -89069,7 +89069,7 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E806" s="5" t="n">
@@ -89275,7 +89275,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">

--- a/output/pdf_financials_xlsx/SF.xlsx
+++ b/output/pdf_financials_xlsx/SF.xlsx
@@ -7068,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.00125</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -7092,19 +7092,19 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>4.4e-05</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.001567</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.008865</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.038314</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.006505</v>
       </c>
       <c r="P112" s="3" t="n">
         <v>0</v>
@@ -37830,7 +37830,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -40717,7 +40721,11 @@
           <t>Proceeds on disposal of property and equipment 6</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -43006,7 +43014,11 @@
           <t>Loss on disposal of property and equipment 6</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -45293,7 +45305,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -55763,7 +55779,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -57092,7 +57112,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SF.xlsx
+++ b/output/pdf_financials_xlsx/SF.xlsx
@@ -1332,13 +1332,13 @@
         <v>-17.573334</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-2.64343</v>
+        <v>-2.307174</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-6.018184</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.31114</v>
+        <v>0.77986</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-1.804277</v>
@@ -1394,13 +1394,13 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.336256</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.091</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1643,7 +1643,7 @@
         <v>-2.64343</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-6.018184</v>
+        <v>-2.436662</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.31114</v>
@@ -1667,10 +1667,10 @@
         <v>-5.697656</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-18.214284</v>
+        <v>-18.007884</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-2.268512</v>
+        <v>-1.474523</v>
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>-0.2064</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-0.7939889999999999</v>
       </c>
       <c r="R21" s="1" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         <v>-17.573334</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.64343</v>
+        <v>-2.307174</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-6.018184</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.31114</v>
+        <v>0.77986</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-1.804277</v>
@@ -2198,13 +2198,13 @@
         <v>-17.443226</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.513014</v>
+        <v>-2.176758</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.997579</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.286148</v>
+        <v>0.804852</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-1.783205</v>
@@ -2348,13 +2348,13 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-14.57436673610226</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>139.8969045726156</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -4278,10 +4278,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.455276</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.162067</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.114847</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.09003800000000001</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>3.090055</v>
       </c>
       <c r="Q110" s="3" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.112016</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -8411,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.112016</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8475,7 +8475,7 @@
         <v>-2.598827</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-8.013247</v>
+        <v>-8.125263</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-2.588768</v>
@@ -31753,7 +31753,11 @@
           <t>Private placement 11</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -36456,7 +36460,11 @@
           <t>Accretion expense 16</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -38139,7 +38147,11 @@
           <t>Proceeds from private placement 12</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -40327,7 +40339,11 @@
           <t>Accretion expense 13</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -42913,7 +42929,11 @@
           <t>Accretion expense 14</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -47301,7 +47321,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -48087,7 +48111,11 @@
           <t>Private placement 10</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -50109,7 +50137,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -52030,7 +52062,11 @@
           <t>Purchase of equipments</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -63659,7 +63695,11 @@
           <t>Net loss from discontinued operations 17</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -80873,7 +80913,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E724" t="inlineStr">
         <is>
           <t>-</t>
@@ -81774,7 +81818,11 @@
           <t>Deferred income tax (recovery) 15</t>
         </is>
       </c>
-      <c r="D733" t="inlineStr"/>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E733" t="inlineStr">
         <is>
           <t>-</t>
@@ -81875,7 +81923,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D734" t="inlineStr"/>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E734" t="inlineStr">
         <is>
           <t>-</t>
@@ -82675,7 +82727,11 @@
           <t>Income tax recovery 16</t>
         </is>
       </c>
-      <c r="D742" t="inlineStr"/>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E742" t="inlineStr">
         <is>
           <t>-</t>
